--- a/results/tables/Tablas_suplementarias_trabajo.xlsx
+++ b/results/tables/Tablas_suplementarias_trabajo.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0,2469</t>
+          <t>0,2474</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0,2161</t>
+          <t>0,2163</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0,2460</t>
+          <t>0,2466</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0,2997</t>
+          <t>0,2999</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0,3024</t>
+          <t>0,3023</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nota: el paso de tratamiento es idéntico bajo criterio ESH y ACC/AHA por construcción (verificado numéricamente) -- una sola fila, no dos. 'n (denominador del paso)' es el número de personas elegibles para ese paso de la cascada; 'n (modelo)' es el número efectivamente ajustado, menor cuando alguna covariable de área no cubre todos los municipios. WAIC y Phi corresponden al modelo FINAL ponderado (pseudo-verosimilitud con ponde_cal normalizado a media 1 dentro de cada municipio; covariables de área seleccionadas por ΔWAIC&lt;=-2, mejora concordante del log-CPO y cero fallos CPO), no al modelo univariado de exploración. Sensibilidad a matriz de vecindad (reina vs. torre), probada en Tratamiento (mayor Phi): WAIC 4205.8 vs 4205.9 (Δ=0.14), Phi 0.453 vs 0.452 (Δ=-0.001). WAIC: Widely Applicable Information Criterion (criterio de selección de modelos, valores menores indican mejor ajuste). Phi: fracción de la varianza espacial explicada por la estructura geográfica (modelo BYM2), de 0 a 1. RMSE: raíz del error cuadrático medio (validación cruzada espacial de 5 pliegues con observados y predicciones agregados mediante ponde_cal). BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2.</t>
+          <t>Nota: el paso de tratamiento es idéntico bajo criterio ESH y ACC/AHA por construcción (verificado numéricamente) -- una sola fila, no dos. 'n (denominador del paso)' es el número de personas elegibles para ese paso de la cascada; 'n (modelo)' es el número efectivamente ajustado, menor cuando alguna covariable de área no cubre todos los municipios. WAIC y Phi corresponden al modelo FINAL ponderado (pseudo-verosimilitud con ponde_cal normalizado a media 1 dentro de cada municipio; covariables de área seleccionadas por ΔWAIC&lt;=-2, mejora concordante del log-CPO y cero fallos CPO), no al modelo univariado de exploración. Sensibilidad a matriz de vecindad (reina vs. torre), probada en Tratamiento (mayor Phi): WAIC 4205.8 vs 4205.9 (Δ=0.14), Phi 0.453 vs 0.452 (Δ=-0.001). WAIC: Widely Applicable Information Criterion (criterio de selección de modelos, valores menores indican mejor ajuste). Phi: fracción de la varianza espacial explicada por la estructura geográfica (modelo BYM2), de 0 a 1. RMSE: raíz del error cuadrático medio (validación cruzada espacial de 5 pliegues con observados y predicciones agregados mediante ponde_cal). El comparador de validación se calcula solo con entrenamiento en cada pliegue. BYM2: modelo espacial bayesiano Besag-York-Mollié tipo 2.</t>
         </is>
       </c>
     </row>
